--- a/documentação/Testes/Caso de Teste/UC34 - MANTER AGENDA  - ROOT.xlsx
+++ b/documentação/Testes/Caso de Teste/UC34 - MANTER AGENDA  - ROOT.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="101">
   <si>
     <r>
       <rPr>
@@ -79,6 +79,9 @@
     <t xml:space="preserve">- Sistema exibe lista de clínicas
 - Cada registro mostra: Nome da clínica e botão "PRÓXIMO"
 - Exibe filtro superior com campo de pesquisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
   </si>
   <si>
     <t xml:space="preserve">CT-02</t>
@@ -480,19 +483,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -620,7 +623,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.22"/>
@@ -670,421 +673,469 @@
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
